--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104496_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104496_W5.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.119300000000001</v>
+        <v>7.5668</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6664</v>
+        <v>4.3978</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4529</v>
+        <v>3.169</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6384</v>
+        <v>5.6366</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5845</v>
+        <v>0.5777</v>
       </c>
       <c r="I2" t="n">
-        <v>5.0539</v>
+        <v>5.059</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1665</v>
+        <v>4.1383</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6101</v>
+        <v>-0.628</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7765</v>
+        <v>4.7663</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4719</v>
+        <v>1.4983</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1946</v>
+        <v>1.2057</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2773</v>
+        <v>0.2926</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7984</v>
+        <v>0.2488</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1785</v>
+        <v>-0.0561</v>
       </c>
       <c r="U2" t="n">
-        <v>0.62</v>
+        <v>0.3049</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0067</v>
+        <v>7.3627</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0713</v>
+        <v>4.4034</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9354</v>
+        <v>2.9592</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1852</v>
+        <v>7.1882</v>
       </c>
       <c r="H3" t="n">
-        <v>3.632</v>
+        <v>3.6277</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5532</v>
+        <v>3.5605</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6228</v>
+        <v>5.6045</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5629</v>
+        <v>2.5511</v>
       </c>
       <c r="L3" t="n">
-        <v>3.06</v>
+        <v>3.0534</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5623</v>
+        <v>1.5837</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0691</v>
+        <v>1.0766</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6321</v>
+        <v>-0.2808</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2148</v>
+        <v>-0.2179</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3404</v>
+        <v>5.9048</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9486</v>
+        <v>3.0886</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3918</v>
+        <v>2.8162</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2823</v>
+        <v>4.1339</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8024</v>
+        <v>1.8239</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4799</v>
+        <v>2.31</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7189</v>
+        <v>3.0961</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4577</v>
+        <v>1.4511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2612</v>
+        <v>1.645</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5634</v>
+        <v>1.0377</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3446</v>
+        <v>0.3727</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2187</v>
+        <v>0.665</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0976</v>
+        <v>-0.0893</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6302</v>
+        <v>-0.2744</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4674</v>
+        <v>0.1851</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8678</v>
+        <v>1.405</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8678</v>
+        <v>1.405</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1631</v>
+        <v>4.2838</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5966</v>
+        <v>1.2313</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5665</v>
+        <v>3.0525</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1443</v>
+        <v>2.2922</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8254</v>
+        <v>1.7954</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3189</v>
+        <v>0.4968</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1332</v>
+        <v>1.6978</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4648</v>
+        <v>1.4372</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6684</v>
+        <v>0.2607</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0111</v>
+        <v>0.5944</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3605</v>
+        <v>0.3583</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6505</v>
+        <v>0.2361</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.849</v>
+        <v>2.0419</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8166</v>
+        <v>0.9495</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0324</v>
+        <v>1.0923</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4141</v>
+        <v>0.8603</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4141</v>
+        <v>0.8603</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8621</v>
+        <v>2.5195</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3246</v>
+        <v>0.4443</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5374</v>
+        <v>2.0753</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2992</v>
+        <v>0.6681</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0274</v>
+        <v>1.712</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2718</v>
+        <v>-1.0439</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0093</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>1.4684</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-1.3931</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2898</v>
+        <v>0.5928</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0954</v>
+        <v>0.2437</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1945</v>
+        <v>0.3492</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2293</v>
+        <v>0.4158</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1221</v>
+        <v>0.369</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1072</v>
+        <v>0.0468</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4141</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8201</v>
+        <v>1.8103</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2745</v>
+        <v>-0.9963</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5457</v>
+        <v>2.8067</v>
       </c>
       <c r="G7" t="n">
-        <v>0.667</v>
+        <v>3.9472</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7172</v>
+        <v>1.071</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0502</v>
+        <v>2.8762</v>
       </c>
       <c r="J7" t="n">
-        <v>0.096</v>
+        <v>3.3384</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4821</v>
+        <v>0.3825</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3861</v>
+        <v>2.9559</v>
       </c>
       <c r="M7" t="n">
-        <v>0.571</v>
+        <v>0.6088</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2351</v>
+        <v>0.6886</v>
       </c>
       <c r="O7" t="n">
-        <v>0.336</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.274</v>
+        <v>0.8223</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1785</v>
+        <v>0.2179</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4525</v>
+        <v>0.6044</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BUTAJEVAS</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5395</v>
+        <v>1.3162</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0051</v>
+        <v>1.0874</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5344</v>
+        <v>0.2288</v>
       </c>
       <c r="G8" t="n">
-        <v>0.861</v>
+        <v>-1.2914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4718</v>
+        <v>-1.0282</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3892</v>
+        <v>-0.2633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0746</v>
+        <v>-1.0237</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.9415</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7864</v>
+        <v>-0.2678</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4718</v>
+        <v>-0.0866</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3145</v>
+        <v>-0.1811</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3215</v>
+        <v>1.6759</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>0.9125</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2519</v>
+        <v>0.7634</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>A. BUTAJEVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3601</v>
+        <v>0.6354</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0362</v>
+        <v>0.0048</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3963</v>
+        <v>0.6306</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9477</v>
+        <v>0.8641</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0663</v>
+        <v>0.4738</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8814</v>
+        <v>0.3903</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3684</v>
+        <v>0.0745</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3912</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9772</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5793</v>
+        <v>0.7896</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6751</v>
+        <v>0.4738</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0958</v>
+        <v>0.3159</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.9488</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6388</v>
+        <v>-0.2287</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.868</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2292</v>
+        <v>-0.159</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2499</v>
+        <v>-2.2015</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.608</v>
+        <v>-0.3956</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.642</v>
+        <v>-1.8059</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8666</v>
+        <v>1.8638</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6538</v>
+        <v>0.6466</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2129</v>
+        <v>1.2172</v>
       </c>
       <c r="J10" t="n">
-        <v>1.917</v>
+        <v>1.9043</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6856</v>
+        <v>0.6755</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0504</v>
+        <v>-0.0405</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3188</v>
+        <v>-0.2717</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9527</v>
+        <v>-3.1715</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.381</v>
+        <v>-3.3337</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5716</v>
+        <v>0.1622</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0469</v>
+        <v>-2.1667</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0069</v>
+        <v>-0.3075</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0399</v>
+        <v>-1.8592</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3938</v>
+        <v>-1.4961</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4311</v>
+        <v>-0.3932</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>-1.1029</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3469</v>
+        <v>-0.6706</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4241</v>
+        <v>0.0857</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0772</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2683</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5232</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2299</v>
+        <v>0.4387</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2934</v>
+        <v>0.3289</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2643</v>
+        <v>-3.317</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0851</v>
+        <v>-2.7737</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1791</v>
+        <v>-0.5433</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9068</v>
+        <v>-1.0525</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7503</v>
+        <v>-1.0217</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1565</v>
+        <v>-0.0309</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4591</v>
+        <v>-1.4149</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-1.4521</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7247</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4477</v>
+        <v>0.3623</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0159</v>
+        <v>0.4305</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4318</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5498</v>
+        <v>0.1696</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5081</v>
+        <v>-0.1233</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0417</v>
+        <v>0.2929</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4</v>
+        <v>-3.6861</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5682</v>
+        <v>-3.5749</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1682</v>
+        <v>-0.1111</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1655</v>
+        <v>-2.9172</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3103</v>
+        <v>-0.7524</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8552</v>
+        <v>-2.1648</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4784</v>
+        <v>-2.4738</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3881</v>
+        <v>-0.7379</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0903</v>
+        <v>-1.7359</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6871</v>
+        <v>-0.4433</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.0144</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7649</v>
+        <v>-0.4289</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5387</v>
+        <v>0.1416</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1785</v>
+        <v>0.037</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3602</v>
+        <v>0.1046</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.3444</v>
+        <v>19.02340000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2086</v>
+        <v>3.583400000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>15.1359</v>
+        <v>15.4402</v>
       </c>
       <c r="G14" t="n">
-        <v>19.1741</v>
+        <v>19.16630000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>8.6585</v>
+        <v>8.6183</v>
       </c>
       <c r="I14" t="n">
-        <v>10.5158</v>
+        <v>10.5479</v>
       </c>
       <c r="J14" t="n">
-        <v>13.7568</v>
+        <v>13.5207</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9486</v>
+        <v>3.8131</v>
       </c>
       <c r="L14" t="n">
-        <v>9.808300000000003</v>
+        <v>9.707799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>5.4173</v>
+        <v>5.6454</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7096</v>
+        <v>4.805700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7074000000000001</v>
+        <v>0.8402000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.5365</v>
+        <v>-4.5525</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2809</v>
+        <v>-19.3488</v>
       </c>
       <c r="R14" t="n">
-        <v>14.744</v>
+        <v>14.796</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7028</v>
+        <v>5.413</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4368</v>
+        <v>2.1569</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2661</v>
+        <v>3.256</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9961000000000002</v>
+        <v>-1.0033</v>
       </c>
       <c r="W14" t="n">
-        <v>7.2954</v>
+        <v>7.254200000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.291600000000001</v>
+        <v>-8.257400000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9417</v>
+        <v>1.7782</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5272</v>
+        <v>2.1472</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5855</v>
+        <v>-0.369</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.3354</v>
+        <v>-1.3414</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2453</v>
+        <v>0.2469</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5807</v>
+        <v>-1.5883</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9052</v>
+        <v>0.8793</v>
       </c>
       <c r="K15" t="n">
-        <v>0.876</v>
+        <v>0.8651</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2407</v>
+        <v>-2.2207</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7573</v>
+        <v>0.5944</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5293</v>
+        <v>0.1784</v>
       </c>
       <c r="U15" t="n">
-        <v>0.228</v>
+        <v>0.416</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6138</v>
+        <v>-0.0061</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4376</v>
+        <v>-0.0325</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0514</v>
+        <v>0.0264</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1994</v>
+        <v>-0.0061</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3202</v>
+        <v>-0.2012</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8791</v>
+        <v>0.1952</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2218</v>
+        <v>0.0372</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6967</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5251</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9776</v>
+        <v>-0.0433</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3764</v>
+        <v>-0.2012</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.354</v>
+        <v>0.1579</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8417</v>
+        <v>-0.2276</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0697</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9233</v>
+        <v>-0.1579</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0104</v>
+        <v>-0.2532</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0322</v>
+        <v>-2.9346</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0219</v>
+        <v>2.6814</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0104</v>
+        <v>-2.1992</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.205</v>
+        <v>-0.327</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1946</v>
+        <v>-1.8721</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0373</v>
+        <v>-1.2432</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0373</v>
+        <v>-0.529</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0477</v>
+        <v>-0.956</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.205</v>
+        <v>0.3871</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>-1.3432</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2268</v>
+        <v>-0.0359</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0696</v>
+        <v>-0.5532</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1573</v>
+        <v>0.5173</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6162</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8046</v>
+        <v>-0.4555</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0791</v>
+        <v>-0.2852</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2745</v>
+        <v>-0.1703</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7484</v>
+        <v>-1.746</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6666</v>
+        <v>0.6718</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.415</v>
+        <v>-2.4178</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0223</v>
+        <v>-0.0412</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6278</v>
+        <v>1.6203</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7261</v>
+        <v>-1.7048</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1074</v>
+        <v>0.2497</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9739</v>
+        <v>-0.1467</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8665</v>
+        <v>0.3964</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0456</v>
+        <v>-1.0172</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9547</v>
+        <v>-0.0814</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9091</v>
+        <v>-0.9359</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6784</v>
+        <v>-1.2486</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8383</v>
+        <v>-0.8017</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1599</v>
+        <v>-0.4468</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9518</v>
+        <v>0.3115</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6793</v>
+        <v>-0.6862</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6311</v>
+        <v>0.9977</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6302</v>
+        <v>-1.5601</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.159</v>
+        <v>-0.1155</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4712</v>
+        <v>-1.4446</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.722</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3133</v>
+        <v>-0.2742</v>
       </c>
       <c r="T19" t="n">
-        <v>0.496</v>
+        <v>-0.3929</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1827</v>
+        <v>0.1187</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2575</v>
+        <v>-1.1483</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1583</v>
+        <v>-0.4643</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4158</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0491</v>
+        <v>-1.0339</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8515</v>
+        <v>-1.8415</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8024</v>
+        <v>0.8076</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3493</v>
+        <v>-0.3637</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5034</v>
+        <v>-1.5103</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1541</v>
+        <v>1.1467</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6998</v>
+        <v>-0.6703</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7567</v>
+        <v>-0.6575</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2692</v>
+        <v>-0.3188</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0259</v>
+        <v>-0.3388</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7048</v>
+        <v>-1.3264</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4246</v>
+        <v>-2.7133</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2802</v>
+        <v>1.3869</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2574</v>
+        <v>-0.6898</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8096</v>
+        <v>-0.8414</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4478</v>
+        <v>0.1516</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3224</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6825</v>
+        <v>-0.697</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0048</v>
+        <v>1.6077</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5798</v>
+        <v>-1.6006</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1272</v>
+        <v>-0.1444</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4526</v>
+        <v>-1.4562</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>2.7316</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9406</v>
+        <v>0.0463</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.747</v>
+        <v>-0.2096</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1936</v>
+        <v>0.2559</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8678</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. FERRANDO</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4437</v>
+        <v>-1.8789</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0596</v>
+        <v>0.2532</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3841</v>
+        <v>-2.1321</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1913</v>
+        <v>-0.506</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3463</v>
+        <v>0.014</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.845</v>
+        <v>-0.52</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7864</v>
+        <v>1.0525</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.3308</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>0.7217</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.405</v>
+        <v>-1.5585</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3463</v>
+        <v>-0.3168</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0586</v>
+        <v>-1.2417</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1183</v>
+        <v>-1.4216</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>-0.7506</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0209</v>
+        <v>-0.671</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>G. FERRANDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.631</v>
+        <v>-2.1793</v>
       </c>
       <c r="E23" t="n">
-        <v>0.168</v>
+        <v>-1.8303</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.799</v>
+        <v>-0.349</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.51</v>
+        <v>-1.1909</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0071</v>
+        <v>-0.3447</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5171</v>
+        <v>-0.8462</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0774</v>
+        <v>-0.7896</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3392</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7382</v>
+        <v>-0.7896</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5875</v>
+        <v>-0.4012</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3321</v>
+        <v>-0.3447</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2554</v>
+        <v>-0.0565</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1625</v>
+        <v>0.1498</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.868</v>
+        <v>0.0975</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2945</v>
+        <v>0.0523</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8514</v>
+        <v>-2.9755</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9704</v>
+        <v>-1.8598</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.881</v>
+        <v>-1.1157</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.307</v>
+        <v>-1.3032</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2857</v>
+        <v>-1.2839</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.7007</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6099</v>
+        <v>-0.6025</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3895</v>
+        <v>0.2579</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.2788</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9546</v>
+        <v>-3.4275</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.781</v>
+        <v>-4.7156</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1736</v>
+        <v>1.2882</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.1964</v>
+        <v>-4.7024</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5383</v>
+        <v>-2.381</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.6581</v>
+        <v>-2.3214</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.5289</v>
+        <v>-4.148</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-2.538</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7945</v>
+        <v>-1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6675</v>
+        <v>-0.5544</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8038999999999999</v>
+        <v>0.157</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8636</v>
+        <v>-0.7114</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>3.4145</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7582</v>
+        <v>-1.1591</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1179</v>
+        <v>-0.8345</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6403</v>
+        <v>-0.3246</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.1962</v>
+        <v>-3.8575</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.2501</v>
+        <v>-2.9237</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0539</v>
+        <v>-0.9339</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.6908</v>
+        <v>-3.1989</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.3823</v>
+        <v>-1.5285</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.3085</v>
+        <v>-1.6704</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.1056</v>
+        <v>-1.5506</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.522</v>
+        <v>-0.7379</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.5835</v>
+        <v>-0.8126</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-1.6483</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1397</v>
+        <v>-0.7906</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.7249</v>
+        <v>-0.8578</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4025</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9344</v>
+        <v>-0.6586</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4245</v>
+        <v>-0.2349</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5099</v>
+        <v>-0.4237</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.3443</v>
+        <v>-16.7472</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.1358</v>
+        <v>-15.4403</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.2084</v>
+        <v>-1.307</v>
       </c>
       <c r="G27" t="n">
-        <v>-19.174</v>
+        <v>-19.1664</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.658200000000001</v>
+        <v>-8.6182</v>
       </c>
       <c r="I27" t="n">
-        <v>-10.5157</v>
+        <v>-10.5479</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.4173</v>
+        <v>-5.6457</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.7097</v>
+        <v>-4.805299999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.7076</v>
+        <v>-0.8402000000000003</v>
       </c>
       <c r="M27" t="n">
-        <v>-13.757</v>
+        <v>-13.5207</v>
       </c>
       <c r="N27" t="n">
-        <v>-3.9487</v>
+        <v>-3.813</v>
       </c>
       <c r="O27" t="n">
-        <v>-9.808100000000001</v>
+        <v>-9.707899999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>4.5365</v>
+        <v>4.552499999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-14.7443</v>
+        <v>-14.7963</v>
       </c>
       <c r="R27" t="n">
-        <v>19.2809</v>
+        <v>19.3487</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.7031</v>
+        <v>-3.1364</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.2662</v>
+        <v>-3.256</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.4368</v>
+        <v>0.1193999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9960000000000002</v>
+        <v>1.0031</v>
       </c>
       <c r="W27" t="n">
-        <v>8.291599999999999</v>
+        <v>8.257399999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.295399999999999</v>
+        <v>-7.2541</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104496_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104496_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.257400000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104496_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-7.2541</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
